--- a/templates/Book3.xlsx
+++ b/templates/Book3.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,10 +27,19 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -39,12 +48,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6E0B4"/>
+        <bgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -52,13 +73,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,128 +467,301 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>PART I - SHIPPING BILL SUMMARY</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>PART II - INVOICE DETAILS</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>PART IV - EXPORT SCHEME DETAILS</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="n"/>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="n"/>
+      <c r="W1" s="1" t="n"/>
+      <c r="X1" s="1" t="n"/>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>PART IV - EXPORT SCHEME DETAILS</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="n"/>
+      <c r="AA1" s="1" t="n"/>
+      <c r="AB1" s="1" t="n"/>
+      <c r="AC1" s="1" t="n"/>
+      <c r="AD1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>A. REF</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>C. VAL DTLS</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>D. ITEM DETAILS</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>A. DRAWBACK &amp; ROSL CLAIM</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
+      <c r="W2" s="2" t="n"/>
+      <c r="X2" s="2" t="n"/>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>M. RODTEP DETAILS</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="n"/>
+      <c r="AA2" s="2" t="n"/>
+      <c r="AB2" s="2" t="n"/>
+      <c r="AC2" s="2" t="n"/>
+      <c r="AD2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Port Code</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
           <t>Shipping Bill No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Shipping Bill Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Invoice No</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Invoice Date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Exchange Rate</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Item No</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>HS Code</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>HSN Code</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Product Description</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>UQC</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Rate</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>FOB</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Invoice Value</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Drawback</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>RODTEP</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Exchange Rate</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>IEC</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>GSTIN</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Port Code</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Source File</t>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Unit Rate</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Item Value (FCY)</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>1.INV SNO</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>2.ITEM SNO</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>3.DBK SNO.</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>4.QTY/WT</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>5.VALUE</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>6.RATE</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>7.DBK AMT</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>8.STALEV</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>9.CENLEV</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>10.ROSCTL AMT</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="n"/>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>1.INVSN</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>2.ITMSN</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>3. QUANTITY</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>4. UQC</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>5. NO. OF UNITS</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>6. VALUE</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="N2:W2"/>
+    <mergeCell ref="Y2:AD2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="N1:W1"/>
+    <mergeCell ref="Y1:AD1"/>
+    <mergeCell ref="D1:M1"/>
+    <mergeCell ref="G2:M2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>